--- a/feedback_forms/016_self_audit_likert_scale_survey--feedback_forms.xlsx
+++ b/feedback_forms/016_self_audit_likert_scale_survey--feedback_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="29" customWidth="1" min="2" max="2"/>
-    <col width="43" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="49" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -515,7 +515,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -525,13 +525,13 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Overall Workplace Culture</t>
+          <t>Overall, the workplace culture is</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -554,7 +554,7 @@
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -571,20 +571,20 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Workplace safety</t>
+          <t>The level of workplace safety is</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -594,13 +594,13 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Job Satisfaction</t>
+          <t>Overall Satisfaction</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -612,58 +612,58 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>feedback_on_culture</t>
+          <t>culture_and_safety</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Overall, my feedback on workplace culture</t>
+          <t>Overall, my feedback on culture and safety</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>feedback_on_safety</t>
+          <t>overall_satisfaction</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Overall, my feedback on workplace safety</t>
+          <t>Overall, I am satisfied with my workplace</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>overall_satisfaction</t>
+          <t>feedback_culture</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Overall, my satisfaction</t>
+          <t>Feedback on my current culture</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,17 +676,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>overall_satisfaction_2</t>
+          <t>feedback_safety</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Overall, my satisfaction</t>
+          <t>Feedback on my current workplace safety</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -704,41 +704,41 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>feedback_safety</t>
+          <t>overall_safety</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Feedback, Safety</t>
+          <t>Overall, I feel safe in my workplace</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>culture_and_safety</t>
+          <t>job_satisfaction_2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Culture and Safety</t>
+          <t>I am satisfied with my job overall</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -750,64 +750,64 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>overall_workplace_safety</t>
+          <t>workplace_satisfaction_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Overall, workplace safety</t>
+          <t>My workplace is satisfying</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>culture_safety</t>
+          <t>feelings_of_ownership</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Overall, Culture and Safety</t>
+          <t>I feel ownership for my work</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>overall_satisfaction_2_2</t>
+          <t>culture_satisfaction</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Overall, my satisfaction</t>
+          <t>I am satisfied with the culture of my workplace</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -819,271 +819,18 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>job_satisfaction_2</t>
+          <t>overall_safety_2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Job Satisfaction</t>
+          <t>Overall Safety 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>workplace_satisfaction</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Workplace Satisfaction</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>job_satisfaction_2</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Job Satisfaction</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>job_ownership_2</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>I feel a sense of ownership for my work</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>workplace_satisfaction_2</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Workplace Satisfaction</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>job_ownership_2</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>I feel a sense of ownership for my work</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>overall_workplace_culture_2</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Overall, Workplace Culture</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>culture_satisfaction</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Culture Satisfaction</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>overall_satisfaction_3</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Overall, my satisfaction</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>overall_satisfaction_3</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Overall, my satisfaction</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>feedback_culture</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Feedback, Culture</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>job_satisfaction_3</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Job Satisfaction</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1098,12 +845,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C116"/>
+  <dimension ref="A1:C60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="37" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +878,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>very_good</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>Very Good</t>
         </is>
       </c>
     </row>
@@ -1148,12 +895,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1165,12 +912,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1182,12 +929,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1199,12 +946,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>very_poor</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>Very Poor</t>
         </is>
       </c>
     </row>
@@ -1216,12 +963,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>strongly_agree</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>Strongly Agree</t>
         </is>
       </c>
     </row>
@@ -1233,12 +980,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>agree</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>Agree</t>
         </is>
       </c>
     </row>
@@ -1250,12 +997,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>disagree</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>Disagree</t>
         </is>
       </c>
     </row>
@@ -1267,29 +1014,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>strongly_disagree</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>Strongly Disagree</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>job_ownership_choices</t>
+          <t>workplace_safety_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>strongly_agree</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>Strongly Agree</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1048,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>agree</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>Agree</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1065,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>neither_agree_nor_disagree</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>Neither Agree nor Disagree</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1082,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>disagree</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>Disagree</t>
         </is>
       </c>
     </row>
@@ -1352,199 +1099,199 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>strongly_disagree</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>Strongly Disagree</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>workplace_safety_choices</t>
+          <t>job_satisfaction_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>Very Satisfied</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>feedback_on_culture_choices</t>
+          <t>job_satisfaction_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>Somewhat Satisfied</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>feedback_on_culture_choices</t>
+          <t>job_satisfaction_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>not_very_satisfied</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>Not Very Satisfied</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>feedback_on_culture_choices</t>
+          <t>job_satisfaction_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>not_very_unsatisfied</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>Not Very Unsatisfied</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>feedback_on_culture_choices</t>
+          <t>job_satisfaction_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>very_unsatisfied</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>Very Unsatisfied</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>feedback_on_culture_choices</t>
+          <t>culture_and_safety_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>strongly_agree</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>Strongly Agree</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>feedback_on_safety_choices</t>
+          <t>culture_and_safety_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>agree</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>Agree</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>feedback_on_safety_choices</t>
+          <t>culture_and_safety_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>neither_agree_nor_disagree</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>Neither Agree nor Disagree</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>feedback_on_safety_choices</t>
+          <t>culture_and_safety_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>disagree</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>Disagree</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>feedback_on_safety_choices</t>
+          <t>culture_and_safety_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>strongly_disagree</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>Strongly Disagree</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>feedback_on_safety_choices</t>
+          <t>overall_satisfaction_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>Very Satisfied</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1303,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>Somewhat Satisfied</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1320,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>not_very_satisfied</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>Not Very Satisfied</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1337,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>not_very_unsatisfied</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>Not Very Unsatisfied</t>
         </is>
       </c>
     </row>
@@ -1607,1474 +1354,522 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>very_unsatisfied</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>Very Unsatisfied</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>overall_satisfaction_choices</t>
+          <t>overall_safety_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>Very Satisfied</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>overall_satisfaction_2_choices</t>
+          <t>overall_safety_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>Somewhat Satisfied</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>overall_satisfaction_2_choices</t>
+          <t>overall_safety_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>not_very_satisfied</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>Not Very Satisfied</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>overall_satisfaction_2_choices</t>
+          <t>overall_safety_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>not_very_unsatisfied</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>Not Very Unsatisfied</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>overall_satisfaction_2_choices</t>
+          <t>overall_safety_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>very_unsatisfied</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>Very Unsatisfied</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>overall_satisfaction_2_choices</t>
+          <t>job_satisfaction_2_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>Very Satisfied</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>feedback_safety_choices</t>
+          <t>job_satisfaction_2_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>Somewhat Satisfied</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>feedback_safety_choices</t>
+          <t>job_satisfaction_2_choices</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>not_very_satisfied</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>Not Very Satisfied</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>feedback_safety_choices</t>
+          <t>job_satisfaction_2_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>not_very_unsatisfied</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>Not Very Unsatisfied</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>feedback_safety_choices</t>
+          <t>job_satisfaction_2_choices</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>very_unsatisfied</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>Very Unsatisfied</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>feedback_safety_choices</t>
+          <t>workplace_satisfaction_2_choices</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>Very Satisfied</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>culture_and_safety_choices</t>
+          <t>workplace_satisfaction_2_choices</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>Somewhat Satisfied</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>culture_and_safety_choices</t>
+          <t>workplace_satisfaction_2_choices</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>not_very_satisfied</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>Not Very Satisfied</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>culture_and_safety_choices</t>
+          <t>workplace_satisfaction_2_choices</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>not_very_unsatisfied</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>Not Very Unsatisfied</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>culture_and_safety_choices</t>
+          <t>workplace_satisfaction_2_choices</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>very_unsatisfied</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>Very Unsatisfied</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>culture_and_safety_choices</t>
+          <t>feelings_of_ownership_choices</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>strongly_agree</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>Strongly Agree</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>overall_workplace_safety_choices</t>
+          <t>feelings_of_ownership_choices</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>agree</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>Agree</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>overall_workplace_safety_choices</t>
+          <t>feelings_of_ownership_choices</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>neither_agree_nor_disagree</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>Neither Agree nor Disagree</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>overall_workplace_safety_choices</t>
+          <t>feelings_of_ownership_choices</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>disagree</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>Disagree</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>overall_workplace_safety_choices</t>
+          <t>feelings_of_ownership_choices</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>strongly_disagree</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>Strongly Disagree</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>overall_workplace_safety_choices</t>
+          <t>culture_satisfaction_choices</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>Very Satisfied</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>culture_safety_choices</t>
+          <t>culture_satisfaction_choices</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>Somewhat Satisfied</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>culture_safety_choices</t>
+          <t>culture_satisfaction_choices</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>not_very_satisfied</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>Not Very Satisfied</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>culture_safety_choices</t>
+          <t>culture_satisfaction_choices</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>not_very_unsatisfied</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>Not Very Unsatisfied</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>culture_safety_choices</t>
+          <t>culture_satisfaction_choices</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>very_unsatisfied</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>Very Unsatisfied</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>culture_safety_choices</t>
+          <t>overall_safety_2_choices</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>Very Satisfied</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>job_satisfaction_2_choices</t>
+          <t>overall_safety_2_choices</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>Somewhat Satisfied</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>job_satisfaction_2_choices</t>
+          <t>overall_safety_2_choices</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>not_very_satisfied</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>Not Very Satisfied</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>job_satisfaction_2_choices</t>
+          <t>overall_safety_2_choices</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>not_very_unsatisfied</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>Not Very Unsatisfied</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>job_satisfaction_2_choices</t>
+          <t>overall_safety_2_choices</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>very_unsatisfied</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>4.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>job_satisfaction_2_choices</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>workplace_satisfaction_choices</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>workplace_satisfaction_choices</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>workplace_satisfaction_choices</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>workplace_satisfaction_choices</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>workplace_satisfaction_choices</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>job_satisfaction_2_choices</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>job_satisfaction_2_choices</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>job_satisfaction_2_choices</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>job_satisfaction_2_choices</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>job_satisfaction_2_choices</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>job_ownership_2_choices</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>job_ownership_2_choices</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>job_ownership_2_choices</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>job_ownership_2_choices</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>job_ownership_2_choices</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>workplace_satisfaction_2_choices</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>workplace_satisfaction_2_choices</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>workplace_satisfaction_2_choices</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>workplace_satisfaction_2_choices</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>workplace_satisfaction_2_choices</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>job_ownership_2_choices</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>job_ownership_2_choices</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>job_ownership_2_choices</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>job_ownership_2_choices</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>job_ownership_2_choices</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>overall_workplace_culture_2_choices</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>overall_workplace_culture_2_choices</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>overall_workplace_culture_2_choices</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>overall_workplace_culture_2_choices</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>overall_workplace_culture_2_choices</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>culture_satisfaction_choices</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>culture_satisfaction_choices</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>culture_satisfaction_choices</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>culture_satisfaction_choices</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>culture_satisfaction_choices</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>overall_satisfaction_3_choices</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>overall_satisfaction_3_choices</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>overall_satisfaction_3_choices</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>overall_satisfaction_3_choices</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>overall_satisfaction_3_choices</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>overall_satisfaction_3_choices</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>overall_satisfaction_3_choices</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>overall_satisfaction_3_choices</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>overall_satisfaction_3_choices</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>overall_satisfaction_3_choices</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>feedback_culture_choices</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>feedback_culture_choices</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>feedback_culture_choices</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>feedback_culture_choices</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>feedback_culture_choices</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>job_satisfaction_3_choices</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>job_satisfaction_3_choices</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>job_satisfaction_3_choices</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>job_satisfaction_3_choices</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>job_satisfaction_3_choices</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>5.0</t>
+          <t>Very Unsatisfied</t>
         </is>
       </c>
     </row>
